--- a/practices/testcases/gara-wave06/ui/TC_STOCK-V2-REPORTS.xlsx
+++ b/practices/testcases/gara-wave06/ui/TC_STOCK-V2-REPORTS.xlsx
@@ -482,7 +482,7 @@
         <v>High</v>
       </c>
       <c r="D3" t="str">
-        <v>Mở tab "Báo cáo tồn kho" — filter mặc định</v>
+        <v>Kiểm tra hiển thị filter mặc định thành công khi mở tab "Báo cáo tồn kho"</v>
       </c>
       <c r="E3" t="str">
         <v>Tenant có data tồn kho</v>
@@ -512,7 +512,7 @@
         <v>High</v>
       </c>
       <c r="D4" t="str">
-        <v>Đổi filter search/kho/ngày → refetch</v>
+        <v>Kiểm tra refetch dữ liệu thành công khi đổi filter search/kho/ngày</v>
       </c>
       <c r="E4" t="str">
         <v>Bảng có data</v>
@@ -543,7 +543,7 @@
         <v>High</v>
       </c>
       <c r="D5" t="str">
-        <v>Bấm "Xem lịch sử" điều hướng đúng mã/kho</v>
+        <v>Kiểm tra điều hướng đúng mã/kho thành công khi bấm "Xem lịch sử"</v>
       </c>
       <c r="E5" t="str">
         <v>Dòng mã PN-18901, kho Kho Chính</v>
@@ -572,7 +572,7 @@
         <v>High</v>
       </c>
       <c r="D6" t="str">
-        <v>Bấm "Xuất file"</v>
+        <v>Kiểm tra xuất file "Báo cáo tồn kho.xlsx" thành công khi bấm "Xuất file"</v>
       </c>
       <c r="E6" t="str">
         <v>Bảng có data</v>
@@ -601,7 +601,7 @@
         <v>High</v>
       </c>
       <c r="D7" t="str">
-        <v>Lỗi tải báo cáo (network/500)</v>
+        <v>Kiểm tra hiển thị lỗi tải báo cáo thất bại với dữ liệu BE trả network/500</v>
       </c>
       <c r="E7" t="str">
         <v>Giả lập lỗi BE</v>
@@ -630,7 +630,7 @@
         <v>High</v>
       </c>
       <c r="D8" t="str">
-        <v>Xuất file khi 0 dòng dữ liệu</v>
+        <v>Kiểm tra disable nút "Xuất file" thành công khi filter không khớp mã nào (0 dòng dữ liệu)</v>
       </c>
       <c r="E8" t="str">
         <v>Filter không khớp mã nào</v>
@@ -688,7 +688,7 @@
         <v>High</v>
       </c>
       <c r="D10" t="str">
-        <v>Tap tile "Tồn kho" trên hub mở StockListPage</v>
+        <v>Kiểm tra mở StockListPage thành công khi tap tile "Tồn kho" trên hub</v>
       </c>
       <c r="E10" t="str">
         <v>Flag Inventory:InventoryV2 ON</v>
@@ -719,7 +719,7 @@
         <v>High</v>
       </c>
       <c r="D11" t="str">
-        <v>Card hiển thị đúng 4 dòng info theo thứ tự</v>
+        <v>Kiểm tra hiển thị đúng thứ tự 4 dòng info trên card với dữ liệu ≥1 sản phẩm tồn</v>
       </c>
       <c r="E11" t="str">
         <v>Có ≥1 sản phẩm tồn</v>
@@ -748,7 +748,7 @@
         <v>High</v>
       </c>
       <c r="D12" t="str">
-        <v>Tap search icon mở SearchPage 3 trạng thái</v>
+        <v>Kiểm tra hiển thị đúng 3 trạng thái SearchPage thành công khi tap search icon</v>
       </c>
       <c r="E12" t="str">
         <v>—</v>
@@ -782,7 +782,7 @@
         <v>High</v>
       </c>
       <c r="D13" t="str">
-        <v>Tap filter icon → chọn Ngày+Kho → Áp dụng</v>
+        <v>Kiểm tra áp dụng filter Ngày+Kho thành công khi tap filter icon</v>
       </c>
       <c r="E13" t="str">
         <v>—</v>
@@ -815,7 +815,7 @@
         <v>High</v>
       </c>
       <c r="D14" t="str">
-        <v>Bấm "Thiết lập lại" trong Filter</v>
+        <v>Kiểm tra reset filter về mặc định thành công khi bấm "Thiết lập lại"</v>
       </c>
       <c r="E14" t="str">
         <v>Đã chọn ngày/kho khác mặc định</v>
@@ -873,7 +873,7 @@
         <v>Medium</v>
       </c>
       <c r="D16" t="str">
-        <v>Filter ngày — chọn ngày hợp lệ</v>
+        <v>Kiểm tra filter ngày thành công với dữ liệu ngày hợp lệ 01/08/2026</v>
       </c>
       <c r="E16" t="str">
         <v>—</v>
@@ -902,7 +902,7 @@
         <v>Medium</v>
       </c>
       <c r="D17" t="str">
-        <v>Filter search — debounce 300ms, LIKE khớp mã/tên</v>
+        <v>Kiểm tra filter search debounce 300ms và LIKE khớp mã/tên thành công</v>
       </c>
       <c r="E17" t="str">
         <v>—</v>
@@ -932,7 +932,7 @@
         <v>Medium</v>
       </c>
       <c r="D18" t="str">
-        <v>Filter kho — multi-select nhiều kho</v>
+        <v>Kiểm tra filter kho multi-select thành công với dữ liệu 2 kho</v>
       </c>
       <c r="E18" t="str">
         <v>2 kho có data</v>
@@ -990,7 +990,7 @@
         <v>Medium</v>
       </c>
       <c r="D20" t="str">
-        <v>GT tồn hiển thị số/0, KHÔNG "Tạm tính"</v>
+        <v>Kiểm tra hiển thị GT tồn dạng số/0 thành công, không hiển thị text "Tạm tính" với dữ liệu mã chưa chạy BQGQ</v>
       </c>
       <c r="E20" t="str">
         <v>Mã PN-18906 chưa chạy BQGQ</v>
@@ -1019,7 +1019,7 @@
         <v>Medium</v>
       </c>
       <c r="D21" t="str">
-        <v>Dòng Tổng geometry 4-cell riêng</v>
+        <v>Kiểm tra hiển thị dòng Tổng đúng geometry 4-cell riêng biệt</v>
       </c>
       <c r="E21" t="str">
         <v>Bảng có data</v>
@@ -1048,7 +1048,7 @@
         <v>Medium</v>
       </c>
       <c r="D22" t="str">
-        <v>Cột "ĐVT chính" hiển thị tên VN, fallback mã khi null</v>
+        <v>Kiểm tra hiển thị cột "ĐVT chính" đúng tên VN, fallback mã khi null</v>
       </c>
       <c r="E22" t="str">
         <v>Mã có mainUnitDisplayName</v>
@@ -1078,7 +1078,7 @@
         <v>Medium</v>
       </c>
       <c r="D23" t="str">
-        <v>Empty state không render dòng Tổng</v>
+        <v>Kiểm tra ẩn dòng Tổng thành công tại empty state khi filter không khớp</v>
       </c>
       <c r="E23" t="str">
         <v>Filter không khớp</v>
@@ -1107,7 +1107,7 @@
         <v>Medium</v>
       </c>
       <c r="D24" t="str">
-        <v>Link "Xem lịch sử" có aria-label riêng theo mã</v>
+        <v>Kiểm tra link "Xem lịch sử" có đúng aria-label riêng theo từng mã</v>
       </c>
       <c r="E24" t="str">
         <v>Bảng có nhiều dòng</v>
@@ -1136,7 +1136,7 @@
         <v>Medium</v>
       </c>
       <c r="D25" t="str">
-        <v>Mobile — Semantics label+value cho InfoRow</v>
+        <v>Kiểm tra semantics label+value đúng cho InfoRow trên Mobile</v>
       </c>
       <c r="E25" t="str">
         <v>Card đang hiển thị</v>
@@ -1194,7 +1194,7 @@
         <v>High</v>
       </c>
       <c r="D27" t="str">
-        <v>garage-owner Web+Mobile truy cập đầy đủ</v>
+        <v>Kiểm tra phân quyền truy cập đầy đủ thành công cho vai trò garage-owner trên cả Web và Mobile</v>
       </c>
       <c r="E27" t="str">
         <v>Tài khoản garage-owner</v>
@@ -1223,7 +1223,7 @@
         <v>High</v>
       </c>
       <c r="D28" t="str">
-        <v>accountant Web+Mobile truy cập đầy đủ</v>
+        <v>Kiểm tra phân quyền truy cập đầy đủ thành công cho vai trò accountant trên cả Web và Mobile</v>
       </c>
       <c r="E28" t="str">
         <v>Tài khoản accountant</v>
@@ -1252,7 +1252,7 @@
         <v>High</v>
       </c>
       <c r="D29" t="str">
-        <v>Mobile không có action "Xem lịch sử"/"Xuất file"</v>
+        <v>Kiểm tra ẩn action "Xem lịch sử"/"Xuất file" thành công trên Mobile</v>
       </c>
       <c r="E29" t="str">
         <v>Mở StockListPage mobile</v>
@@ -1310,7 +1310,7 @@
         <v>High</v>
       </c>
       <c r="D31" t="str">
-        <v>Cùng mã 2 kho → 2 dòng riêng biệt</v>
+        <v>Kiểm tra hiển thị 2 dòng riêng biệt thành công với dữ liệu cùng mã tồn ở 2 kho</v>
       </c>
       <c r="E31" t="str">
         <v>Mã PN-18901 tồn ở 2 kho</v>
@@ -1339,7 +1339,7 @@
         <v>High</v>
       </c>
       <c r="D32" t="str">
-        <v>SL=0 nhưng GT≠0 vẫn hiển thị (hide-rule OR)</v>
+        <v>Kiểm tra hiển thị dòng thành công theo hide-rule OR với dữ liệu SL=0 nhưng GT≠0</v>
       </c>
       <c r="E32" t="str">
         <v>Mã PN-18907</v>
@@ -1368,7 +1368,7 @@
         <v>High</v>
       </c>
       <c r="D33" t="str">
-        <v>Sau PRC chạy xong, GT tồn cập nhật đúng</v>
+        <v>Kiểm tra GT tồn cập nhật đúng thành công sau khi PRC chạy xong</v>
       </c>
       <c r="E33" t="str">
         <v>Mã vừa được PRC tính giá</v>
@@ -1397,7 +1397,7 @@
         <v>High</v>
       </c>
       <c r="D34" t="str">
-        <v>Flag ON → 2 tab V1 bị ẩn khỏi menu</v>
+        <v>Kiểm tra ẩn 2 tab V1 khỏi menu thành công khi feature flag Inventory:InventoryV2 đang ON</v>
       </c>
       <c r="E34" t="str">
         <v>Flag Inventory:InventoryV2 ON</v>
@@ -1426,7 +1426,7 @@
         <v>High</v>
       </c>
       <c r="D35" t="str">
-        <v>Tenant isolation — 2 tenant khác nhau chỉ thấy dữ liệu garage của mình</v>
+        <v>Kiểm tra tenant isolation thành công — 2 tenant khác nhau chỉ thấy đúng dữ liệu garage của mình ở cả 3 báo cáo</v>
       </c>
       <c r="E35" t="str">
         <v>Tenant A và Tenant B đều có data tồn kho</v>
@@ -1486,7 +1486,7 @@
         <v>High</v>
       </c>
       <c r="D37" t="str">
-        <v>Mở tab "Báo cáo NXT" — filter mặc định tháng hiện tại</v>
+        <v>Kiểm tra hiển thị filter mặc định tháng hiện tại thành công khi mở tab "Báo cáo NXT"</v>
       </c>
       <c r="E37" t="str">
         <v>—</v>
@@ -1516,7 +1516,7 @@
         <v>High</v>
       </c>
       <c r="D38" t="str">
-        <v>Đổi filter search/kho/khoảng ngày → refetch</v>
+        <v>Kiểm tra refetch dữ liệu thành công khi đổi filter search/kho/khoảng ngày</v>
       </c>
       <c r="E38" t="str">
         <v>Bảng có data</v>
@@ -1545,7 +1545,7 @@
         <v>High</v>
       </c>
       <c r="D39" t="str">
-        <v>Bấm "Xuất file"</v>
+        <v>Kiểm tra xuất file "Báo cáo nhập xuất tồn.xlsx" thành công khi bấm "Xuất file"</v>
       </c>
       <c r="E39" t="str">
         <v>Bảng có data</v>
@@ -1574,7 +1574,7 @@
         <v>High</v>
       </c>
       <c r="D40" t="str">
-        <v>Click "Mã SP nội bộ" khi productId có giá trị (Blocked — chờ backend hoàn thiện field productId, hiện BE luôn trả null)</v>
+        <v>Kiểm tra điều hướng thành công khi click "Mã SP nội bộ" với dữ liệu productId có giá trị (Blocked — chờ backend hoàn thiện field productId, hiện BE luôn trả null)</v>
       </c>
       <c r="E40" t="str">
         <v>productId != null (giả định BE đã hoàn thiện, hiện tại KHÔNG thực thi được)</v>
@@ -1603,7 +1603,7 @@
         <v>High</v>
       </c>
       <c r="D41" t="str">
-        <v>Lỗi tải báo cáo</v>
+        <v>Kiểm tra hiển thị lỗi tải báo cáo thất bại với dữ liệu BE lỗi</v>
       </c>
       <c r="E41" t="str">
         <v>Giả lập lỗi BE</v>
@@ -1632,7 +1632,7 @@
         <v>High</v>
       </c>
       <c r="D42" t="str">
-        <v>productId = null → hiển thị text thường, không link (hành vi hiện tại)</v>
+        <v>Kiểm tra hiển thị text thường không phải link thành công với dữ liệu productId = null (hành vi hiện tại)</v>
       </c>
       <c r="E42" t="str">
         <v>Data hiện tại</v>
@@ -1661,7 +1661,7 @@
         <v>Medium</v>
       </c>
       <c r="D43" t="str">
-        <v>0 dòng khớp filter — empty state</v>
+        <v>Kiểm tra hiển thị empty state thành công khi 0 dòng khớp filter</v>
       </c>
       <c r="E43" t="str">
         <v>Filter không khớp</v>
@@ -1719,7 +1719,7 @@
         <v>Medium</v>
       </c>
       <c r="D45" t="str">
-        <v>Khoảng ngày — fromDate &gt; toDate</v>
+        <v>Kiểm tra validate khoảng ngày thất bại khi fromDate &gt; toDate</v>
       </c>
       <c r="E45" t="str">
         <v>—</v>
@@ -1748,7 +1748,7 @@
         <v>Medium</v>
       </c>
       <c r="D46" t="str">
-        <v>Filter kho — multi-select, rỗng = tất cả</v>
+        <v>Kiểm tra filter kho trả về tất cả kho thành công khi không chọn kho nào</v>
       </c>
       <c r="E46" t="str">
         <v>—</v>
@@ -1777,7 +1777,7 @@
         <v>Medium</v>
       </c>
       <c r="D47" t="str">
-        <v>Filter search — debounce 300ms</v>
+        <v>Kiểm tra filter search debounce 300ms thành công</v>
       </c>
       <c r="E47" t="str">
         <v>—</v>
@@ -1835,7 +1835,7 @@
         <v>Medium</v>
       </c>
       <c r="D49" t="str">
-        <v>Header bảng 2 tầng bắt buộc</v>
+        <v>Kiểm tra hiển thị đúng header bảng 2 tầng bắt buộc</v>
       </c>
       <c r="E49" t="str">
         <v>Bảng có data</v>
@@ -1864,7 +1864,7 @@
         <v>Medium</v>
       </c>
       <c r="D50" t="str">
-        <v>Cột Giá trị có hậu tố "đ", cột SL không có</v>
+        <v>Kiểm tra hiển thị đúng hậu tố "đ" cho cột Giá trị, không hậu tố cho cột Số lượng</v>
       </c>
       <c r="E50" t="str">
         <v>Bảng có data</v>
@@ -1894,7 +1894,7 @@
         <v>Medium</v>
       </c>
       <c r="D51" t="str">
-        <v>Bảng viewport-fixed, overflow-x-auto</v>
+        <v>Kiểm tra bảng giữ viewport-fixed và scroll ngang thành công khi resize màn hình hẹp</v>
       </c>
       <c r="E51" t="str">
         <v>Màn hình hẹp</v>
@@ -1923,7 +1923,7 @@
         <v>Medium</v>
       </c>
       <c r="D52" t="str">
-        <v>Prefill khoảng ngày tính động (không hardcode)</v>
+        <v>Kiểm tra prefill khoảng ngày tính động theo ngày hiện tại thành công (không hardcode)</v>
       </c>
       <c r="E52" t="str">
         <v>Mở tab ngày 04/08/2026</v>
@@ -1952,7 +1952,7 @@
         <v>Medium</v>
       </c>
       <c r="D53" t="str">
-        <v>Loading = skeleton table, giữ page header</v>
+        <v>Kiểm tra hiển thị loading state dạng skeleton table thành công, giữ nguyên page header</v>
       </c>
       <c r="E53" t="str">
         <v>—</v>
@@ -2010,7 +2010,7 @@
         <v>High</v>
       </c>
       <c r="D55" t="str">
-        <v>garage-owner truy cập đầy đủ</v>
+        <v>Kiểm tra phân quyền truy cập đầy đủ thành công cho vai trò garage-owner tại tab NXT</v>
       </c>
       <c r="E55" t="str">
         <v>Tài khoản garage-owner</v>
@@ -2039,7 +2039,7 @@
         <v>High</v>
       </c>
       <c r="D56" t="str">
-        <v>accountant truy cập đầy đủ</v>
+        <v>Kiểm tra phân quyền truy cập đầy đủ thành công cho vai trò accountant tại tab NXT</v>
       </c>
       <c r="E56" t="str">
         <v>Tài khoản accountant</v>
@@ -2097,7 +2097,7 @@
         <v>High</v>
       </c>
       <c r="D58" t="str">
-        <v>Cùng mã 2 kho → 2 dòng riêng</v>
+        <v>Kiểm tra hiển thị 2 dòng riêng biệt thành công với dữ liệu cùng mã ở 2 kho</v>
       </c>
       <c r="E58" t="str">
         <v>Mã PN-18901 ở 2 kho</v>
@@ -2126,7 +2126,7 @@
         <v>High</v>
       </c>
       <c r="D59" t="str">
-        <v>OB import trong khoảng lọc → cộng vào Nhập kho</v>
+        <v>Kiểm tra cộng đúng OB import vào nhóm Nhập kho thành công (không cộng vào Đầu kỳ)</v>
       </c>
       <c r="E59" t="str">
         <v>OB import ngày 15/07/2026, filter 01/07-31/07/2026</v>
@@ -2155,7 +2155,7 @@
         <v>High</v>
       </c>
       <c r="D60" t="str">
-        <v>Mã chưa BQGQ → GT Xuất=0, GT Đầu/Nhập là số thật</v>
+        <v>Kiểm tra hiển thị GT Xuất=0 và GT Đầu/Nhập là số thật thành công với dữ liệu mã chưa chạy BQGQ</v>
       </c>
       <c r="E60" t="str">
         <v>Mã PN-18906</v>
@@ -2184,7 +2184,7 @@
         <v>High</v>
       </c>
       <c r="D61" t="str">
-        <v>Đối chiếu Cuối kỳ NXT khớp Tồn-đến-ngày (M6)</v>
+        <v>Kiểm tra đối chiếu Cuối kỳ NXT khớp đúng Tồn-đến-ngày (M6) thành công với dữ liệu cùng ngày</v>
       </c>
       <c r="E61" t="str">
         <v>Cùng ngày X</v>
@@ -2213,7 +2213,7 @@
         <v>High</v>
       </c>
       <c r="D62" t="str">
-        <v>Sau PRC chạy xong, GT Xuất chuyển từ 0 sang giá trị thực</v>
+        <v>Kiểm tra GT Xuất chuyển từ 0 sang giá trị thực thành công sau khi PRC chạy xong</v>
       </c>
       <c r="E62" t="str">
         <v>Mã vừa PRC</v>
@@ -2271,7 +2271,7 @@
         <v>High</v>
       </c>
       <c r="D64" t="str">
-        <v>Click "Xem lịch sử" điều hướng full-page (không modal)</v>
+        <v>Kiểm tra điều hướng full-page thành công (không modal) khi click "Xem lịch sử"</v>
       </c>
       <c r="E64" t="str">
         <v>Từ M6</v>
@@ -2300,7 +2300,7 @@
         <v>High</v>
       </c>
       <c r="D65" t="str">
-        <v>Auto-fill khoảng ngày mặc định = tháng hiện tại</v>
+        <v>Kiểm tra auto-fill khoảng ngày mặc định thành công theo tháng hiện tại</v>
       </c>
       <c r="E65" t="str">
         <v>Mở màn ngày 04/08/2026</v>
@@ -2329,7 +2329,7 @@
         <v>High</v>
       </c>
       <c r="D66" t="str">
-        <v>Bảng running hiển thị đúng theo phiếu</v>
+        <v>Kiểm tra bảng running hiển thị đúng theo từng phiếu với dữ liệu ≥3 phiếu trong khoảng</v>
       </c>
       <c r="E66" t="str">
         <v>Có ≥3 phiếu nhập/xuất trong khoảng</v>
@@ -2358,7 +2358,7 @@
         <v>High</v>
       </c>
       <c r="D67" t="str">
-        <v>Đổi khoảng ngày → refetch</v>
+        <v>Kiểm tra refetch dữ liệu thành công khi đổi khoảng ngày</v>
       </c>
       <c r="E67" t="str">
         <v>—</v>
@@ -2387,7 +2387,7 @@
         <v>High</v>
       </c>
       <c r="D68" t="str">
-        <v>Click "Số phiếu" (phiếu nhập)</v>
+        <v>Kiểm tra điều hướng đúng chi tiết phiếu nhập thành công khi click "Số phiếu"</v>
       </c>
       <c r="E68" t="str">
         <v>Dòng slipType=RECEIPT</v>
@@ -2416,7 +2416,7 @@
         <v>High</v>
       </c>
       <c r="D69" t="str">
-        <v>Click "Số phiếu" (phiếu xuất)</v>
+        <v>Kiểm tra điều hướng đúng chi tiết phiếu xuất thành công khi click "Số phiếu"</v>
       </c>
       <c r="E69" t="str">
         <v>Dòng slipType=DELIVERY</v>
@@ -2445,7 +2445,7 @@
         <v>High</v>
       </c>
       <c r="D70" t="str">
-        <v>Bấm "Xuất file"</v>
+        <v>Kiểm tra xuất file "Báo cáo thẻ kho.xlsx" thành công khi bấm "Xuất file"</v>
       </c>
       <c r="E70" t="str">
         <v>Bảng có data</v>
@@ -2474,7 +2474,7 @@
         <v>High</v>
       </c>
       <c r="D71" t="str">
-        <v>Bấm "Đóng" quay lại M6</v>
+        <v>Kiểm tra điều hướng quay lại M6 thành công khi bấm "Đóng"</v>
       </c>
       <c r="E71" t="str">
         <v>—</v>
@@ -2503,7 +2503,7 @@
         <v>High</v>
       </c>
       <c r="D72" t="str">
-        <v>Không có biến động trong khoảng (EC-3)</v>
+        <v>Kiểm tra trả HTTP 200 với content rỗng thành công khi không có biến động trong khoảng lọc</v>
       </c>
       <c r="E72" t="str">
         <v>Mã không có phiếu trong khoảng lọc</v>
@@ -2562,7 +2562,7 @@
         <v>Medium</v>
       </c>
       <c r="D74" t="str">
-        <v>Range-picker không cho chọn ngược (nếu UI giới hạn)</v>
+        <v>Kiểm tra chặn chọn ngược Đến&lt;Từ trên range-picker thành công</v>
       </c>
       <c r="E74" t="str">
         <v>—</v>
@@ -2620,7 +2620,7 @@
         <v>Medium</v>
       </c>
       <c r="D76" t="str">
-        <v>KHÔNG hiển thị filter/chip Kho</v>
+        <v>Kiểm tra ẩn filter/chip Kho thành công tại màn Thẻ kho</v>
       </c>
       <c r="E76" t="str">
         <v>Màn đã mở</v>
@@ -2649,7 +2649,7 @@
         <v>Medium</v>
       </c>
       <c r="D77" t="str">
-        <v>Không cho chọn mã trực tiếp</v>
+        <v>Kiểm tra chặn chọn mã trực tiếp thành công tại màn Thẻ kho</v>
       </c>
       <c r="E77" t="str">
         <v>Màn đã mở</v>
@@ -2678,7 +2678,7 @@
         <v>Medium</v>
       </c>
       <c r="D78" t="str">
-        <v>"Số phiếu" style link, "Mã SP nội bộ" text thường</v>
+        <v>Kiểm tra hiển thị đúng style link cho "Số phiếu" và text thường cho "Mã SP nội bộ"</v>
       </c>
       <c r="E78" t="str">
         <v>Bảng có data</v>
@@ -2707,7 +2707,7 @@
         <v>Medium</v>
       </c>
       <c r="D79" t="str">
-        <v>Focus vào &lt;h1&gt; khi route mount</v>
+        <v>Kiểm tra focus tự động vào tiêu đề &lt;h1&gt; thành công khi route mount</v>
       </c>
       <c r="E79" t="str">
         <v>Điều hướng vào màn</v>
@@ -2765,7 +2765,7 @@
         <v>High</v>
       </c>
       <c r="D81" t="str">
-        <v>garage-owner truy cập đầy đủ</v>
+        <v>Kiểm tra phân quyền truy cập đầy đủ thành công cho vai trò garage-owner tại màn Thẻ kho</v>
       </c>
       <c r="E81" t="str">
         <v>Tài khoản garage-owner</v>
@@ -2794,7 +2794,7 @@
         <v>High</v>
       </c>
       <c r="D82" t="str">
-        <v>accountant truy cập đầy đủ</v>
+        <v>Kiểm tra phân quyền truy cập đầy đủ thành công cho vai trò accountant tại màn Thẻ kho</v>
       </c>
       <c r="E82" t="str">
         <v>Tài khoản accountant</v>
@@ -2852,7 +2852,7 @@
         <v>High</v>
       </c>
       <c r="D84" t="str">
-        <v>Running balance đúng: Cuối kỳ dòng trước = Đầu kỳ dòng sau</v>
+        <v>Kiểm tra running balance đúng thành công: Cuối kỳ dòng trước khớp Đầu kỳ dòng sau</v>
       </c>
       <c r="E84" t="str">
         <v>≥3 phiếu trong khoảng</v>
@@ -2881,7 +2881,7 @@
         <v>High</v>
       </c>
       <c r="D85" t="str">
-        <v>Đầu kỳ dòng đầu tra đúng sổ tồn</v>
+        <v>Kiểm tra Đầu kỳ dòng đầu tiên tra đúng sổ tồn thành công</v>
       </c>
       <c r="E85" t="str">
         <v>Có biến động trước khoảng lọc</v>
@@ -2910,7 +2910,7 @@
         <v>High</v>
       </c>
       <c r="D86" t="str">
-        <v>Reconciliation — Cuối kỳ dòng cuối ngày D = tồn cuối ngày D (M6)</v>
+        <v>Kiểm tra reconciliation thành công: Cuối kỳ dòng cuối ngày D khớp tồn cuối ngày D (M6)</v>
       </c>
       <c r="E86" t="str">
         <v>Cùng ngày D</v>
@@ -2939,7 +2939,7 @@
         <v>High</v>
       </c>
       <c r="D87" t="str">
-        <v>Mã chưa BQGQ → GT Xuất=0, GT Cuối = GT Đầu+Nhập</v>
+        <v>Kiểm tra hiển thị GT Xuất=0 và GT Cuối = GT Đầu+Nhập thành công với dữ liệu mã chưa chạy BQGQ</v>
       </c>
       <c r="E87" t="str">
         <v>Mã PN-18906</v>
@@ -2968,7 +2968,7 @@
         <v>High</v>
       </c>
       <c r="D88" t="str">
-        <v>Sau PRC chạy xong, GT Xuất các dòng cập nhật đúng</v>
+        <v>Kiểm tra GT Xuất các dòng cập nhật đúng thành công sau khi PRC chạy xong</v>
       </c>
       <c r="E88" t="str">
         <v>Mã vừa PRC</v>
